--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -470,28 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.65599</v>
+        <v>17.11267</v>
       </c>
       <c r="D2" t="n">
-        <v>16.88662</v>
+        <v>16.86468</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76079</v>
+        <v>16.88402</v>
       </c>
       <c r="F2" t="n">
-        <v>55.47459</v>
+        <v>42.1591</v>
       </c>
       <c r="G2" t="n">
-        <v>42.40018</v>
+        <v>0.05111</v>
       </c>
       <c r="H2" t="n">
-        <v>85.42318</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05052</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.88475</v>
+        <v>1.88541</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.78502</v>
+        <v>16.85365</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31333</v>
+        <v>16.41299</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61778</v>
+        <v>16.49233</v>
       </c>
       <c r="F3" t="n">
-        <v>56.1187</v>
+        <v>42.16184</v>
       </c>
       <c r="G3" t="n">
-        <v>42.58104</v>
+        <v>0.05137</v>
       </c>
       <c r="H3" t="n">
-        <v>85.26786</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05027</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.79755</v>
+        <v>1.83577</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67089</v>
+        <v>16.67376</v>
       </c>
       <c r="D4" t="n">
-        <v>15.94499</v>
+        <v>16.41466</v>
       </c>
       <c r="E4" t="n">
-        <v>16.86136</v>
+        <v>16.43846</v>
       </c>
       <c r="F4" t="n">
-        <v>55.29095</v>
+        <v>42.70811</v>
       </c>
       <c r="G4" t="n">
-        <v>41.98516</v>
+        <v>0.05035</v>
       </c>
       <c r="H4" t="n">
-        <v>84.47790999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05062</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.87213</v>
+        <v>1.79376</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.80395</v>
+        <v>16.7308</v>
       </c>
       <c r="D5" t="n">
-        <v>16.69147</v>
+        <v>16.31565</v>
       </c>
       <c r="E5" t="n">
-        <v>16.50532</v>
+        <v>16.53353</v>
       </c>
       <c r="F5" t="n">
-        <v>55.92728</v>
+        <v>42.21145</v>
       </c>
       <c r="G5" t="n">
-        <v>41.86443</v>
+        <v>0.05183</v>
       </c>
       <c r="H5" t="n">
-        <v>84.70018</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05013</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.81679</v>
+        <v>1.83584</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.70524</v>
+        <v>16.81566</v>
       </c>
       <c r="D6" t="n">
-        <v>16.48051</v>
+        <v>16.7377</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8024</v>
+        <v>16.77885</v>
       </c>
       <c r="F6" t="n">
-        <v>56.28762</v>
+        <v>42.23713</v>
       </c>
       <c r="G6" t="n">
-        <v>42.59152</v>
+        <v>0.05067</v>
       </c>
       <c r="H6" t="n">
-        <v>84.81413999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05044</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.84082</v>
+        <v>1.79894</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90656</v>
+        <v>16.58897</v>
       </c>
       <c r="D7" t="n">
-        <v>17.04559</v>
+        <v>16.32245</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76283</v>
+        <v>16.44094</v>
       </c>
       <c r="F7" t="n">
-        <v>55.72919</v>
+        <v>42.78855</v>
       </c>
       <c r="G7" t="n">
-        <v>42.38198</v>
+        <v>0.05094</v>
       </c>
       <c r="H7" t="n">
-        <v>84.74301</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0498</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.85183</v>
+        <v>1.81188</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.90101</v>
+        <v>16.58434</v>
       </c>
       <c r="D8" t="n">
-        <v>16.53851</v>
+        <v>16.16973</v>
       </c>
       <c r="E8" t="n">
-        <v>16.34232</v>
+        <v>16.47879</v>
       </c>
       <c r="F8" t="n">
-        <v>55.24127</v>
+        <v>42.82465</v>
       </c>
       <c r="G8" t="n">
-        <v>42.19241</v>
+        <v>0.05077</v>
       </c>
       <c r="H8" t="n">
-        <v>85.75587</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05014</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.78848</v>
+        <v>1.83084</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.95348</v>
+        <v>16.88895</v>
       </c>
       <c r="D9" t="n">
-        <v>16.6623</v>
+        <v>16.52337</v>
       </c>
       <c r="E9" t="n">
-        <v>17.27305</v>
+        <v>16.55431</v>
       </c>
       <c r="F9" t="n">
-        <v>55.16803</v>
+        <v>41.78958</v>
       </c>
       <c r="G9" t="n">
-        <v>42.75515</v>
+        <v>0.05113</v>
       </c>
       <c r="H9" t="n">
-        <v>85.3969</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.05085</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.83188</v>
+        <v>1.80062</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.82827</v>
+        <v>17.077</v>
       </c>
       <c r="D10" t="n">
-        <v>16.58074</v>
+        <v>16.79124</v>
       </c>
       <c r="E10" t="n">
-        <v>16.76947</v>
+        <v>16.79954</v>
       </c>
       <c r="F10" t="n">
-        <v>56.10611</v>
+        <v>42.42256</v>
       </c>
       <c r="G10" t="n">
-        <v>43.33355</v>
+        <v>0.04891</v>
       </c>
       <c r="H10" t="n">
-        <v>83.65797000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05137</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.83317</v>
+        <v>1.8257</v>
       </c>
     </row>
     <row r="11">
@@ -760,25 +696,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -796,28 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.82099</v>
+        <v>16.70503</v>
       </c>
       <c r="D12" t="n">
-        <v>16.62434</v>
+        <v>16.35786</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6381</v>
+        <v>16.60202</v>
       </c>
       <c r="F12" t="n">
-        <v>54.61553</v>
+        <v>42.7057</v>
       </c>
       <c r="G12" t="n">
-        <v>41.73101</v>
+        <v>0.0507</v>
       </c>
       <c r="H12" t="n">
-        <v>84.50651999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05102</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.79563</v>
+        <v>1.81512</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.13629</v>
+        <v>16.73909</v>
       </c>
       <c r="D13" t="n">
-        <v>16.83926</v>
+        <v>16.30134</v>
       </c>
       <c r="E13" t="n">
-        <v>16.64949</v>
+        <v>16.70187</v>
       </c>
       <c r="F13" t="n">
-        <v>54.59822</v>
+        <v>42.3746</v>
       </c>
       <c r="G13" t="n">
-        <v>43.29922</v>
+        <v>0.05121</v>
       </c>
       <c r="H13" t="n">
-        <v>84.42359999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.84359</v>
+        <v>1.83246</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.53043</v>
+        <v>16.63127</v>
       </c>
       <c r="D14" t="n">
-        <v>16.54362</v>
+        <v>16.37076</v>
       </c>
       <c r="E14" t="n">
-        <v>16.58676</v>
+        <v>16.62034</v>
       </c>
       <c r="F14" t="n">
-        <v>56.51498</v>
+        <v>42.13169</v>
       </c>
       <c r="G14" t="n">
-        <v>42.02547</v>
+        <v>0.05115</v>
       </c>
       <c r="H14" t="n">
-        <v>84.94726</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.04977</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.84455</v>
+        <v>1.8467</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.78699</v>
+        <v>16.84841</v>
       </c>
       <c r="D15" t="n">
-        <v>16.35425</v>
+        <v>16.54065</v>
       </c>
       <c r="E15" t="n">
-        <v>16.23926</v>
+        <v>16.62183</v>
       </c>
       <c r="F15" t="n">
-        <v>55.66719</v>
+        <v>42.7791</v>
       </c>
       <c r="G15" t="n">
-        <v>42.55544</v>
+        <v>0.05078</v>
       </c>
       <c r="H15" t="n">
-        <v>84.94458</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.05011</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.81376</v>
+        <v>1.80645</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.3404</v>
+        <v>16.71448</v>
       </c>
       <c r="D16" t="n">
-        <v>16.50699</v>
+        <v>16.52396</v>
       </c>
       <c r="E16" t="n">
-        <v>16.40907</v>
+        <v>16.59942</v>
       </c>
       <c r="F16" t="n">
-        <v>55.4821</v>
+        <v>43.04702</v>
       </c>
       <c r="G16" t="n">
-        <v>44.09358</v>
+        <v>0.05069</v>
       </c>
       <c r="H16" t="n">
-        <v>85.49238</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.05136</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.79689</v>
+        <v>1.82541</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.06152</v>
+        <v>17.0407</v>
       </c>
       <c r="D17" t="n">
-        <v>16.66815</v>
+        <v>16.56365</v>
       </c>
       <c r="E17" t="n">
-        <v>17.06457</v>
+        <v>17.01746</v>
       </c>
       <c r="F17" t="n">
-        <v>55.88478</v>
+        <v>41.60662</v>
       </c>
       <c r="G17" t="n">
-        <v>43.10819</v>
+        <v>0.0502</v>
       </c>
       <c r="H17" t="n">
-        <v>86.43498</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05133</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.83904</v>
+        <v>1.81899</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.66208</v>
+        <v>17.06354</v>
       </c>
       <c r="D18" t="n">
-        <v>16.69579</v>
+        <v>16.77283</v>
       </c>
       <c r="E18" t="n">
-        <v>16.29454</v>
+        <v>17.05531</v>
       </c>
       <c r="F18" t="n">
-        <v>54.61045</v>
+        <v>42.7396</v>
       </c>
       <c r="G18" t="n">
-        <v>42.52214</v>
+        <v>0.05073</v>
       </c>
       <c r="H18" t="n">
-        <v>85.48931</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05017</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.80241</v>
+        <v>1.81956</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.91528</v>
+        <v>16.6622</v>
       </c>
       <c r="D19" t="n">
-        <v>16.52017</v>
+        <v>16.47806</v>
       </c>
       <c r="E19" t="n">
-        <v>16.23986</v>
+        <v>16.53038</v>
       </c>
       <c r="F19" t="n">
-        <v>55.42015</v>
+        <v>42.03358</v>
       </c>
       <c r="G19" t="n">
-        <v>41.69307</v>
+        <v>0.05007</v>
       </c>
       <c r="H19" t="n">
-        <v>86.08695</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05052</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.82907</v>
+        <v>1.82675</v>
       </c>
     </row>
     <row r="20">
@@ -1044,28 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.13603</v>
+        <v>16.84296</v>
       </c>
       <c r="D20" t="n">
-        <v>16.83707</v>
+        <v>16.52813</v>
       </c>
       <c r="E20" t="n">
-        <v>16.45457</v>
+        <v>16.60101</v>
       </c>
       <c r="F20" t="n">
-        <v>54.5257</v>
+        <v>42.9808</v>
       </c>
       <c r="G20" t="n">
-        <v>42.97138</v>
+        <v>0.05056</v>
       </c>
       <c r="H20" t="n">
-        <v>84.44479</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05045</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.82517</v>
+        <v>1.83747</v>
       </c>
     </row>
     <row r="21">
@@ -1086,12 +958,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -1103,23 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.64661</v>
+        <v>15.84601</v>
       </c>
       <c r="D22" t="n">
-        <v>15.90707</v>
+        <v>15.57054</v>
       </c>
       <c r="E22" t="n">
-        <v>16.31992</v>
+        <v>15.57934</v>
       </c>
       <c r="F22" t="n">
-        <v>21.99497</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.30272</v>
+        <v>245.11596</v>
       </c>
     </row>
     <row r="23">
@@ -1129,19 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.62064</v>
+        <v>15.76913</v>
       </c>
       <c r="D23" t="n">
-        <v>15.9537</v>
+        <v>15.45723</v>
       </c>
       <c r="E23" t="n">
-        <v>16.27324</v>
+        <v>15.61915</v>
       </c>
       <c r="F23" t="n">
-        <v>21.95029</v>
-      </c>
-      <c r="G23" t="n">
-        <v>34.34526</v>
+        <v>256.84873</v>
       </c>
     </row>
     <row r="24">
@@ -1151,19 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.3865</v>
+        <v>15.67877</v>
       </c>
       <c r="D24" t="n">
-        <v>15.71749</v>
+        <v>15.31416</v>
       </c>
       <c r="E24" t="n">
-        <v>16.52544</v>
+        <v>15.64689</v>
       </c>
       <c r="F24" t="n">
-        <v>22.17239</v>
-      </c>
-      <c r="G24" t="n">
-        <v>33.75769</v>
+        <v>254.89762</v>
       </c>
     </row>
     <row r="25">
@@ -1173,19 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.62686</v>
+        <v>15.51646</v>
       </c>
       <c r="D25" t="n">
-        <v>16.21434</v>
+        <v>15.45058</v>
       </c>
       <c r="E25" t="n">
-        <v>16.61039</v>
+        <v>15.46157</v>
       </c>
       <c r="F25" t="n">
-        <v>21.89842</v>
-      </c>
-      <c r="G25" t="n">
-        <v>34.03345</v>
+        <v>251.90125</v>
       </c>
     </row>
     <row r="26">
@@ -1195,19 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.35634</v>
+        <v>15.78334</v>
       </c>
       <c r="D26" t="n">
-        <v>16.02796</v>
+        <v>15.75819</v>
       </c>
       <c r="E26" t="n">
-        <v>16.47543</v>
+        <v>15.76398</v>
       </c>
       <c r="F26" t="n">
-        <v>22.02388</v>
-      </c>
-      <c r="G26" t="n">
-        <v>33.63169</v>
+        <v>259.39416</v>
       </c>
     </row>
     <row r="27">
@@ -1217,19 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.72109</v>
+        <v>15.70123</v>
       </c>
       <c r="D27" t="n">
-        <v>15.92625</v>
+        <v>15.57134</v>
       </c>
       <c r="E27" t="n">
-        <v>16.28767</v>
+        <v>15.67059</v>
       </c>
       <c r="F27" t="n">
-        <v>21.82432</v>
-      </c>
-      <c r="G27" t="n">
-        <v>33.71816</v>
+        <v>256.72633</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.53553</v>
+        <v>15.83605</v>
       </c>
       <c r="D28" t="n">
-        <v>15.97756</v>
+        <v>15.71107</v>
       </c>
       <c r="E28" t="n">
-        <v>16.38387</v>
+        <v>15.82606</v>
       </c>
       <c r="F28" t="n">
-        <v>21.9486</v>
-      </c>
-      <c r="G28" t="n">
-        <v>34.24087</v>
+        <v>253.64247</v>
       </c>
     </row>
     <row r="29">
@@ -1261,19 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.83993</v>
+        <v>15.72887</v>
       </c>
       <c r="D29" t="n">
-        <v>16.40416</v>
+        <v>15.4525</v>
       </c>
       <c r="E29" t="n">
-        <v>16.51851</v>
+        <v>15.57976</v>
       </c>
       <c r="F29" t="n">
-        <v>21.48478</v>
-      </c>
-      <c r="G29" t="n">
-        <v>33.60761</v>
+        <v>254.69978</v>
       </c>
     </row>
     <row r="30">
@@ -1283,60 +1126,42 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.97185</v>
+        <v>15.823</v>
       </c>
       <c r="D30" t="n">
-        <v>16.30602</v>
+        <v>15.36873</v>
       </c>
       <c r="E30" t="n">
-        <v>16.38073</v>
+        <v>15.60187</v>
       </c>
       <c r="F30" t="n">
-        <v>21.9125</v>
-      </c>
-      <c r="G30" t="n">
-        <v>34.20755</v>
+        <v>252.23471</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1348,32 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.7534</v>
+        <v>17.31546</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08216</v>
+        <v>15.94965</v>
       </c>
       <c r="E32" t="n">
-        <v>0.60984</v>
+        <v>16.08069</v>
       </c>
       <c r="F32" t="n">
-        <v>0.96856</v>
+        <v>21.30691</v>
       </c>
       <c r="G32" t="n">
-        <v>0.10804</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00742</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09493</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12669</v>
+        <v>33.49349</v>
       </c>
     </row>
     <row r="33">
@@ -1383,28 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.74955</v>
+        <v>16.88041</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0804</v>
+        <v>15.84687</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5984</v>
+        <v>16.48954</v>
       </c>
       <c r="F33" t="n">
-        <v>0.94847</v>
+        <v>21.72766</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1104</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00751</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09285</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.12692</v>
+        <v>34.23027</v>
       </c>
     </row>
     <row r="34">
@@ -1414,28 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.75535</v>
+        <v>16.78071</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08011</v>
+        <v>16.08682</v>
       </c>
       <c r="E34" t="n">
-        <v>0.60598</v>
+        <v>16.4393</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9573199999999999</v>
+        <v>21.83517</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11117</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09431</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.12853</v>
+        <v>34.80758</v>
       </c>
     </row>
     <row r="35">
@@ -1445,28 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.73811</v>
+        <v>16.76168</v>
       </c>
       <c r="D35" t="n">
-        <v>0.07954</v>
+        <v>16.1184</v>
       </c>
       <c r="E35" t="n">
-        <v>0.60239</v>
+        <v>16.38067</v>
       </c>
       <c r="F35" t="n">
-        <v>0.96666</v>
+        <v>21.82188</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11123</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09329999999999999</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.12633</v>
+        <v>34.60979</v>
       </c>
     </row>
     <row r="36">
@@ -1476,28 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.74755</v>
+        <v>16.5759</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08123</v>
+        <v>15.97418</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61089</v>
+        <v>16.31163</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9587</v>
+        <v>21.60322</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10481</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00749</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09091</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.12776</v>
+        <v>33.42343</v>
       </c>
     </row>
     <row r="37">
@@ -1507,28 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.74368</v>
+        <v>16.42077</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08162999999999999</v>
+        <v>16.09232</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6116200000000001</v>
+        <v>16.39177</v>
       </c>
       <c r="F37" t="n">
-        <v>0.96507</v>
+        <v>21.84065</v>
       </c>
       <c r="G37" t="n">
-        <v>0.10677</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09365</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.12746</v>
+        <v>34.59768</v>
       </c>
     </row>
     <row r="38">
@@ -1538,28 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7489400000000001</v>
+        <v>16.33394</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08031000000000001</v>
+        <v>15.74367</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6039600000000001</v>
+        <v>16.21033</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9614200000000001</v>
+        <v>22.18729</v>
       </c>
       <c r="G38" t="n">
-        <v>0.10832</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09222</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.12769</v>
+        <v>34.49876</v>
       </c>
     </row>
     <row r="39">
@@ -1569,28 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.74668</v>
+        <v>17.07475</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08076</v>
+        <v>16.16854</v>
       </c>
       <c r="E39" t="n">
-        <v>0.60195</v>
+        <v>16.61482</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9749</v>
+        <v>21.4769</v>
       </c>
       <c r="G39" t="n">
-        <v>0.10994</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09525</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.123</v>
+        <v>34.81212</v>
       </c>
     </row>
     <row r="40">
@@ -1600,28 +1353,843 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.73468</v>
+        <v>16.4535</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0808</v>
+        <v>15.82211</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6044</v>
+        <v>16.25952</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9620300000000001</v>
+        <v>22.1441</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1096</v>
-      </c>
-      <c r="H40" t="n">
+        <v>34.49685</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.76825</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.3994</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.50915</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.29871</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.00114</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.54995</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.10948</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.24408</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.25379</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.81513</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.79552</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.91948</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.45956</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.58526</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.02605</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.31479</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.65895</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.29045</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.81936</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.15355</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.26961</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.94829</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.19294</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.059</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.1514</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.79371</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.03453</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.20628</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.66923</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.11543</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.54087</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.87553</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.37321</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.47004</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.42529</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.36143</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.18932</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.20803</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.1606</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.92291</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.62677</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.10096</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.30196</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.55112</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.24185</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5994699999999999</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.0954</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.60889</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.12578</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60195</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.12525</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.58627</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.09171</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61782</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.11586</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60519</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.08625</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61154</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.1124</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60398</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.12146</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.60751</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.10817</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6033500000000001</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.10652</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.61093</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.11845</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61549</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.10618</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.60287</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.09456</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.61319</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.14318</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60363</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.11825</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.60715</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.10831</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.59587</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.13559</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.59681</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.10776</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.74386</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08094999999999999</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.60536</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.94399</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12764</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08225</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6035199999999999</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.95201</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10993</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09445000000000001</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12727</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.7528899999999999</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08094</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.61578</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.96698</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10896</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09276</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12524</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.7567199999999999</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08012</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61288</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.95322</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10953</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12566</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.75842</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08072</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.95713</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11116</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09483999999999999</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12776</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.74664</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08096</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.60719</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.97423</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11034</v>
+      </c>
+      <c r="H77" t="n">
         <v>0.00759</v>
       </c>
-      <c r="I40" t="n">
-        <v>0.09248000000000001</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12456</v>
+      <c r="I77" t="n">
+        <v>0.09295</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12902</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.75351</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.07963000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60183</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.96371</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10895</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09055000000000001</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12546</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.74903</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08068</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60279</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.93833</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11102</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12419</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.75105</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.07973</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6110100000000001</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.98314</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09346</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12553</v>
       </c>
     </row>
   </sheetData>
